--- a/data/trans_orig/IP07A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41499</t>
+          <t>41729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>52615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70830</t>
+          <t>71432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90687</t>
+          <t>90357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57004</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>71333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76558</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122610</t>
+          <t>123470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145238</t>
+          <t>144571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>21964</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48621</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68537</t>
+          <t>68582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85421</t>
+          <t>86646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66095</t>
+          <t>66585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64160</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78907</t>
+          <t>78645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119225</t>
+          <t>119722</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>140703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67067</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>91880</t>
+          <t>91605</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>141591</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>175819</t>
+          <t>175983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>178312</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>207167</t>
+          <t>207503</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216336</t>
+          <t>216933</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>403622</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>444268</t>
+          <t>444202</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>47537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>27845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67663</t>
+          <t>67768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87310</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39892</t>
+          <t>39226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48348</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64336</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48975</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65095</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103535</t>
+          <t>103354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125436</t>
+          <t>125069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>47300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>54851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81637</t>
+          <t>81041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99223</t>
+          <t>98486</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>766</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>20726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>44141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>61256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97697</t>
+          <t>96080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120132</t>
+          <t>118495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>139701</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>175810</t>
+          <t>177557</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>172597</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>202895</t>
+          <t>202068</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>189451</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>216150</t>
+          <t>217487</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>411319</t>
+          <t>409532</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>20916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38477</t>
+          <t>39198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40112</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>42845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55504</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>86366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106201</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>60750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>50663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66933</t>
+          <t>67344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>56169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73596</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111510</t>
+          <t>112456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134488</t>
+          <t>135353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52875</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47362</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60835</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91805</t>
+          <t>91684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109840</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37101</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43383</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>74772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51977</t>
+          <t>52034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68987</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113793</t>
+          <t>115068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137992</t>
+          <t>139214</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65392</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91831</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95342</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>142948</t>
+          <t>144112</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>179003</t>
+          <t>181989</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>205433</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>235299</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>214060</t>
+          <t>214285</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>244691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>429540</t>
+          <t>427074</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>471547</t>
+          <t>472398</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
